--- a/stories/arbres/TREE-COL-015.xlsx
+++ b/stories/arbres/TREE-COL-015.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Adam est avec papa, dans le jardin. Adam a envie de jouer. papa est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Adam écoute papa. Adam entend les mots : attendre, puis parler.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On se tient la main. papa dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On se tient la main.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6331,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On range un objet. papa dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6469,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On range un objet.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11124,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On dit merci. papa dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11262,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On dit merci.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-015.xlsx
+++ b/stories/arbres/TREE-COL-015.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Adam est avec papa, dans le jardin. Adam a envie de jouer. papa est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Adam écoute papa. Adam entend les mots : attendre, puis parler.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Adam a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2597,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2765,7 @@
           <t>narrateur|Adam rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2933,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3101,7 @@
           <t>narrateur|Adam rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3437,7 @@
           <t>narrateur|Adam rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3773,7 @@
           <t>narrateur|Adam a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3965,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
           <t>narrateur|Adam rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4469,7 @@
           <t>narrateur|Adam rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4805,7 @@
           <t>narrateur|Adam rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4973,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5141,7 @@
           <t>narrateur|Adam a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5333,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5501,7 @@
           <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5669,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5837,7 @@
           <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6173,7 @@
           <t>narrateur|Adam rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6866,7 @@
           <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7058,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7226,7 @@
           <t>narrateur|Adam a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7418,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7586,7 @@
           <t>narrateur|Adam rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7754,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7922,7 @@
           <t>narrateur|Adam rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8090,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8258,7 @@
           <t>narrateur|Adam rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8426,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8594,7 @@
           <t>narrateur|Adam a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8786,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8954,7 @@
           <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9290,7 @@
           <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9626,7 @@
           <t>narrateur|Adam rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +9962,7 @@
           <t>narrateur|Adam a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10154,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10265,6 +10322,7 @@
           <t>narrateur|Adam rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10658,7 @@
           <t>narrateur|Adam rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +10994,7 @@
           <t>narrateur|Adam rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11331,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11515,7 @@
           <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11687,7 @@
           <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11879,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12047,7 @@
           <t>narrateur|Adam a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12239,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12407,7 @@
           <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12575,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12743,7 @@
           <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12911,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13079,7 @@
           <t>narrateur|Adam rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13247,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13415,7 @@
           <t>narrateur|Adam a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13607,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13775,7 @@
           <t>narrateur|Adam rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14111,7 @@
           <t>narrateur|Adam rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14447,7 @@
           <t>narrateur|Adam rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14783,7 @@
           <t>narrateur|Adam a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +14975,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15143,7 @@
           <t>narrateur|Adam rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15479,7 @@
           <t>narrateur|Adam rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15815,7 @@
           <t>narrateur|Adam rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +15983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16026,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16241,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-015.xlsx
+++ b/stories/arbres/TREE-COL-015.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tour de parole — dans le jardin</t>
+          <t>La trace d'argent d'Aniss</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, une trace d'argent brille sur la pierre. Aniss veut raconter l'escargot. Il lève la main, il attend, puis il parle, avec papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Adam est avec papa, dans le jardin. Adam a envie de jouer. papa est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Adam écoute papa. Adam entend les mots : attendre, puis parler.</t>
+          <t>Le volet du salon claque une fois. Une odeur de menthe entre. Les bottes jaunes d'Aniss gouttent dans l'entrée. Une petite flaque brille, tout ronde. Dehors, une pierre est encore mouillée. Une trace d'argent y brille, toute fine. C'est un escargot, tout lent. La soupe sent bon, dans la cuisine. Papa coupe la menthe, tout près. Tu as vu tes bottes, Aniss ? Elles sont mouillées. La pierre brille, dehors. En ce moment, Aniss est à la fenêtre. Il a une chose à dire. Papa parle encore de la soupe. Aniss lève la main. Il attend. On lève la main. On attend. Puis on parle. C'est bientôt ton tour. L'escargot a une trace. Bravo. Tu as attendu. Le volet ne claque plus. La trace d'argent reste sur la pierre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,39 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Adam est avec papa, dans le jardin. Adam a envie de jouer. papa est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Adam écoute papa. Adam entend les mots : attendre, puis parler.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le volet du salon claque une fois.
+narrateur|Une odeur de menthe entre.
+narrateur|Les bottes jaunes d'Aniss gouttent dans l'entrée.
+narrateur|Une petite flaque brille, tout ronde.
+narrateur|Dehors, une pierre est encore mouillée.
+narrateur|Une trace d'argent y brille, toute fine.
+narrateur|C'est un escargot, tout lent.
+narrateur|La soupe sent bon, dans la cuisine.
+narrateur|Papa coupe la menthe, tout près.
+maman|Tu as vu tes bottes, Aniss ?
+enfant-m|Elles sont mouillées.
+papa|La pierre brille, dehors.
+narrateur|En ce moment, Aniss est à la fenêtre.
+narrateur|Il a une chose à dire.
+narrateur|Papa parle encore de la soupe.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+maman|On lève la main.
+maman|On attend.
+maman|Puis on parle.
+papa|C'est bientôt ton tour.
+enfant-m|L'escargot a une trace.
+papa|Bravo.
+papa|Tu as attendu.
+narrateur|Le volet ne claque plus.
+narrateur|La trace d'argent reste sur la pierre.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>volet,menthe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1394,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Où va Aniss, maintenant ? La cuisine, le jardin, ou la chambre ? On s'écoute. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1558,11 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Où va Aniss, maintenant ?
+papa|La cuisine, le jardin, ou la chambre ?
+maman|On s'écoute.
+maman|On attend.
+maman|Puis on parle.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On se tient la main. Je suis là. On reste ensemble.</t>
+          <t>Aniss pousse la porte de la cuisine. La vapeur de la soupe chatouille le nez. Un verre d'eau tient des tiges de menthe. La nappe à carreaux est un peu froissée. Moi, je raconte la soupe. Papa parle, tout près du bol. Aniss a une chose à dire. Il lève la main. Il attend. L'escargot a brillé, dehors. Oui. C'est ton tour. Tu as attendu. On lève la main. On attend. Puis on parle. Une goutte de menthe tombe dans l'eau. Le bois de la table est lisse, un peu chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1730,30 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Adam va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On se tient la main.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss pousse la porte de la cuisine.
+narrateur|La vapeur de la soupe chatouille le nez.
+narrateur|Un verre d'eau tient des tiges de menthe.
+narrateur|La nappe à carreaux est un peu froissée.
+papa|Moi, je raconte la soupe.
+narrateur|Papa parle, tout près du bol.
+narrateur|Aniss a une chose à dire.
+narrateur|Il lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a brillé, dehors.
+maman|Oui. C'est ton tour.
+maman|Tu as attendu.
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Une goutte de menthe tombe dans l'eau.
+narrateur|Le bois de la table est lisse, un peu chaud.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>soupe,menthe</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Tour de parole.</t>
+          <t>Aniss veut parler, dans la cuisine. Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1870,7 +1934,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Tour de parole.</t>
+          <t>narrateur|Aniss veut parler, dans la cuisine.
+papa|Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1898,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>Oui. On lève la main. On attend. Puis on parle. Aniss souffle un peu. Sa main redescend, tout doux. J'ai attendu. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2042,7 +2107,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>papa|Oui.
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss souffle un peu.
+narrateur|Sa main redescend, tout doux.
+enfant-m|J'ai attendu.
+maman|Bravo.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2070,7 +2143,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On joue. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2234,7 +2307,11 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2262,7 +2339,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
+          <t>Aniss prend les cubes en bois. Un cube rouge fait clic. Un cube jaune sent le pin. Moi, je raconte la tour. Papa parle. Aniss lève la main. Il attend. C'est ton tour. Une maison pour l'escargot. Oui. Merci d'avoir attendu. On attend. Puis on parle. Aniss pose un cube, tout droit. Un cube attrape un reflet de menthe. On est encore dans la cuisine. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2402,10 +2479,30 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Aniss prend les cubes en bois.
+narrateur|Un cube rouge fait clic.
+narrateur|Un cube jaune sent le pin.
+papa|Moi, je raconte la tour.
+narrateur|Papa parle.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Une maison pour l'escargot.
+maman|Oui. Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss pose un cube, tout droit.
+narrateur|Un cube attrape un reflet de menthe.
+narrateur|On est encore dans la cuisine.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2430,7 +2527,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2594,7 +2691,10 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2622,7 +2722,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Des miettes dorées restent sur la table. Les oiseaux parlent déjà, tout loin. Aniss a encore les cubes, dans la cuisine. Un cube jaune attrape le soleil sur la table. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2762,10 +2862,29 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Des miettes dorées restent sur la table.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Aniss a encore les cubes, dans la cuisine.
+narrateur|Un cube jaune attrape le soleil sur la table.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2790,7 +2909,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le matin, dans la cuisine. Il a joué avec les cubes. Bravo, Aniss. C'est du bon travail. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2930,7 +3049,14 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le matin, dans la cuisine.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2958,7 +3084,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Aniss a encore les cubes, dans la cuisine. Un cube fait un clic, tout petit, près du bol. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3098,7 +3224,22 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Aniss a encore les cubes, dans la cuisine.
+narrateur|Un cube fait un clic, tout petit, près du bol.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3126,7 +3267,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu après la sieste, dans la cuisine. Il a joué avec les cubes. Bravo, Aniss. C'est du bon travail. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3266,7 +3407,14 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu après la sieste, dans la cuisine.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3294,7 +3442,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Aniss a encore les cubes, dans la cuisine. La lampe allonge l'ombre des cubes. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3434,10 +3582,29 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Aniss a encore les cubes, dans la cuisine.
+narrateur|La lampe allonge l'ombre des cubes.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3462,7 +3629,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le soir, dans la cuisine. Il a joué avec les cubes. Bravo, Aniss. C'est du bon travail. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3602,7 +3769,14 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le soir, dans la cuisine.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3630,7 +3804,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Aniss ouvre le livre. La page sent le papier, un peu sec. Un dessin d'escargot est là, tout gris. Moi, je lis d'abord. Maman lit jusqu'au bout. Aniss lève la main. Il attend. Il a une coquille ronde. Oui. C'est ton tour. On a attendu. Puis on parle. Aniss caresse la page, tout léger. Bravo, Aniss. Une miette reste au bord de la page. On est encore dans la cuisine. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3770,10 +3944,30 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Aniss ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Un dessin d'escargot est là, tout gris.
+maman|Moi, je lis d'abord.
+narrateur|Maman lit jusqu'au bout.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|Il a une coquille ronde.
+papa|Oui. C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+narrateur|Aniss caresse la page, tout léger.
+maman|Bravo, Aniss.
+narrateur|Une miette reste au bord de la page.
+narrateur|On est encore dans la cuisine.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3798,7 +3992,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3962,7 +4156,10 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3990,7 +4187,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Des miettes dorées restent sur la table. Les oiseaux parlent déjà, tout loin. Aniss a encore le livre, dans la cuisine. Une miette reste collée sur la page. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4130,10 +4327,29 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Des miettes dorées restent sur la table.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Aniss a encore le livre, dans la cuisine.
+narrateur|Une miette reste collée sur la page.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4158,7 +4374,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le matin, dans la cuisine. Il a joué avec le livre. Bravo, Aniss. C'est du bon travail. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4298,7 +4514,14 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le matin, dans la cuisine.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4326,7 +4549,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Aniss a encore le livre, dans la cuisine. Le livre est un peu chaud, comme la nappe. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4466,7 +4689,22 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Aniss a encore le livre, dans la cuisine.
+narrateur|Le livre est un peu chaud, comme la nappe.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4494,7 +4732,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu après la sieste, dans la cuisine. Il a joué avec le livre. Bravo, Aniss. C'est du bon travail. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4634,7 +4872,14 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu après la sieste, dans la cuisine.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4662,7 +4907,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Aniss a encore le livre, dans la cuisine. L'escargot du livre brille sous la lampe. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4802,10 +5047,29 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Aniss a encore le livre, dans la cuisine.
+narrateur|L'escargot du livre brille sous la lampe.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4830,7 +5094,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le soir, dans la cuisine. Il a joué avec le livre. Bravo, Aniss. C'est du bon travail. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4970,7 +5234,14 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le soir, dans la cuisine.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -4998,7 +5269,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+          <t>Aniss prend la dînette. Une petite assiette sonne, tout creux. Une cuillère miniature est encore tiède. Moi, je sers la soupe imaginaire. Papa parle. Aniss lève la main. Il attend. Une feuille pour l'escargot ? Oui. C'est ton tour. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Aniss pose la petite assiette, tout doux. La petite casserole est près du vrai bol. On est encore dans la cuisine. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5138,10 +5409,31 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Aniss prend la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+papa|Moi, je sers la soupe imaginaire.
+narrateur|Papa parle.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|Une feuille pour l'escargot ?
+maman|Oui. C'est ton tour.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo.
+papa|Tu as attendu ton tour.
+narrateur|Aniss pose la petite assiette, tout doux.
+narrateur|La petite casserole est près du vrai bol.
+narrateur|On est encore dans la cuisine.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5166,7 +5458,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5330,7 +5622,10 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5358,7 +5653,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Des miettes dorées restent sur la table. Les oiseaux parlent déjà, tout loin. Aniss a encore la dînette, dans la cuisine. La petite casserole sent encore la menthe. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5498,10 +5793,29 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Des miettes dorées restent sur la table.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Aniss a encore la dînette, dans la cuisine.
+narrateur|La petite casserole sent encore la menthe.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5526,7 +5840,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le matin, dans la cuisine. Il a joué avec la dînette. Bravo, Aniss. C'est du bon travail. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5666,7 +5980,14 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le matin, dans la cuisine.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5694,7 +6015,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Aniss a encore la dînette, dans la cuisine. Une cuillère miniature tremble près du bol. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5834,7 +6155,22 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Aniss a encore la dînette, dans la cuisine.
+narrateur|Une cuillère miniature tremble près du bol.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5862,7 +6198,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu après la sieste, dans la cuisine. Il a joué avec la dînette. Bravo, Aniss. C'est du bon travail. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6002,7 +6338,14 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu après la sieste, dans la cuisine.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6030,7 +6373,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Aniss a encore la dînette, dans la cuisine. La dînette fait un tout petit ding. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6170,10 +6513,29 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Aniss a encore la dînette, dans la cuisine.
+narrateur|La dînette fait un tout petit ding.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6198,7 +6560,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le soir, dans la cuisine. Il a joué avec la dînette. Bravo, Aniss. C'est du bon travail. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6338,7 +6700,14 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le soir, dans la cuisine.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6366,7 +6735,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Aniss pose un pied dans l'herbe. L'herbe est froide, encore mouillée. La pierre garde une trace d'argent. Une abeille passe, tout bas. Moi, je raconte l'abeille. Maman parle jusqu'au bout. Aniss lève la main. Il attend. L'escargot est sur la pierre. Oui. Merci d'avoir attendu. On attend. Puis on parle. Aniss se penche, tout doux. La trace d'argent brille encore. Bravo, Aniss. Tu as levé la main.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6506,11 +6875,29 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Adam va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On range un objet.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Aniss pose un pied dans l'herbe.
+narrateur|L'herbe est froide, encore mouillée.
+narrateur|La pierre garde une trace d'argent.
+narrateur|Une abeille passe, tout bas.
+maman|Moi, je raconte l'abeille.
+narrateur|Maman parle jusqu'au bout.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot est sur la pierre.
+papa|Oui. Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss se penche, tout doux.
+narrateur|La trace d'argent brille encore.
+maman|Bravo, Aniss.
+maman|Tu as levé la main.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>oiseau,herbe</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6535,7 +6922,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Tour de parole.</t>
+          <t>Aniss lève la main, dans l'herbe. Et après, on attend ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6691,7 +7078,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Tour de parole.</t>
+          <t>narrateur|Aniss lève la main, dans l'herbe.
+maman|Et après, on attend ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6719,7 +7107,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>Oui. On attend. Puis on parle. Aniss essuie une goutte sur son genou. J'attends mon tour. Bravo, Aniss. La pierre est à toi, et le tour aussi.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6863,7 +7251,13 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>maman|Oui.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Aniss essuie une goutte sur son genou.
+enfant-m|J'attends mon tour.
+papa|Bravo, Aniss.
+papa|La pierre est à toi, et le tour aussi.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6891,7 +7285,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On joue. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7055,7 +7449,11 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7083,7 +7481,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
+          <t>Aniss prend les cubes en bois. Un cube rouge fait clic. Un cube jaune sent le pin. Moi, je raconte la tour. Papa parle. Aniss lève la main. Il attend. C'est ton tour. Une maison pour l'escargot. Oui. Merci d'avoir attendu. On attend. Puis on parle. Aniss pose un cube, tout droit. L'herbe tache un cube, tout vert. On est encore dans le jardin. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7223,10 +7621,30 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Aniss prend les cubes en bois.
+narrateur|Un cube rouge fait clic.
+narrateur|Un cube jaune sent le pin.
+papa|Moi, je raconte la tour.
+narrateur|Papa parle.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Une maison pour l'escargot.
+maman|Oui. Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss pose un cube, tout droit.
+narrateur|L'herbe tache un cube, tout vert.
+narrateur|On est encore dans le jardin.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7251,7 +7669,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7415,7 +7833,10 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7443,7 +7864,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Des miettes dorées restent sur la table. Les oiseaux parlent déjà, tout loin. Aniss a encore les cubes, dans le jardin. L'herbe mouille un cube, tout vert. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7583,10 +8004,29 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Des miettes dorées restent sur la table.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Aniss a encore les cubes, dans le jardin.
+narrateur|L'herbe mouille un cube, tout vert.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7611,7 +8051,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le matin, dans le jardin. Il a joué avec les cubes. Bravo, Aniss. C'est du bon travail. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7751,7 +8191,14 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le matin, dans le jardin.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7779,7 +8226,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Aniss a encore les cubes, dans le jardin. Un cube sèche au soleil, près de la pierre. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7919,7 +8366,22 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Aniss a encore les cubes, dans le jardin.
+narrateur|Un cube sèche au soleil, près de la pierre.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7947,7 +8409,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu après la sieste, dans le jardin. Il a joué avec les cubes. Bravo, Aniss. C'est du bon travail. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8087,7 +8549,14 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu après la sieste, dans le jardin.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8115,7 +8584,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Aniss a encore les cubes, dans le jardin. Un cube garde une goutte, toute ronde. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8255,10 +8724,29 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Aniss a encore les cubes, dans le jardin.
+narrateur|Un cube garde une goutte, toute ronde.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8283,7 +8771,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le soir, dans le jardin. Il a joué avec les cubes. Bravo, Aniss. C'est du bon travail. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8423,7 +8911,14 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le soir, dans le jardin.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8451,7 +8946,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Aniss ouvre le livre. La page sent le papier, un peu sec. Un dessin d'escargot est là, tout gris. Moi, je lis d'abord. Maman lit jusqu'au bout. Aniss lève la main. Il attend. Il a une coquille ronde. Oui. C'est ton tour. On a attendu. Puis on parle. Aniss caresse la page, tout léger. Bravo, Aniss. Une vraie feuille sert de marque-page. On est encore dans le jardin. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8591,10 +9086,30 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Aniss ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Un dessin d'escargot est là, tout gris.
+maman|Moi, je lis d'abord.
+narrateur|Maman lit jusqu'au bout.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|Il a une coquille ronde.
+papa|Oui. C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+narrateur|Aniss caresse la page, tout léger.
+maman|Bravo, Aniss.
+narrateur|Une vraie feuille sert de marque-page.
+narrateur|On est encore dans le jardin.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8619,7 +9134,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8783,7 +9298,10 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8811,7 +9329,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Des miettes dorées restent sur la table. Les oiseaux parlent déjà, tout loin. Aniss a encore le livre, dans le jardin. Une feuille vraie marque encore la page. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8951,10 +9469,29 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Des miettes dorées restent sur la table.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Aniss a encore le livre, dans le jardin.
+narrateur|Une feuille vraie marque encore la page.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8979,7 +9516,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le matin, dans le jardin. Il a joué avec le livre. Bravo, Aniss. C'est du bon travail. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9119,7 +9656,14 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le matin, dans le jardin.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9147,7 +9691,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Aniss a encore le livre, dans le jardin. Le livre sent l'herbe, un peu. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9287,7 +9831,22 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Aniss a encore le livre, dans le jardin.
+narrateur|Le livre sent l'herbe, un peu.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9315,7 +9874,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu après la sieste, dans le jardin. Il a joué avec le livre. Bravo, Aniss. C'est du bon travail. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9455,7 +10014,14 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu après la sieste, dans le jardin.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9483,7 +10049,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Aniss a encore le livre, dans le jardin. Un oiseau chante. Le livre reste ouvert. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9623,10 +10189,30 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Aniss a encore le livre, dans le jardin.
+narrateur|Un oiseau chante.
+narrateur|Le livre reste ouvert.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9651,7 +10237,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le soir, dans le jardin. Il a joué avec le livre. Bravo, Aniss. C'est du bon travail. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9791,7 +10377,14 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le soir, dans le jardin.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9819,7 +10412,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+          <t>Aniss prend la dînette. Une petite assiette sonne, tout creux. Une cuillère miniature est encore tiède. Moi, je sers la soupe imaginaire. Papa parle. Aniss lève la main. Il attend. Une feuille pour l'escargot ? Oui. C'est ton tour. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Aniss pose la petite assiette, tout doux. Une goutte perle au bord de l'assiette. On est encore dans le jardin. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9959,10 +10552,31 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Aniss prend la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+papa|Moi, je sers la soupe imaginaire.
+narrateur|Papa parle.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|Une feuille pour l'escargot ?
+maman|Oui. C'est ton tour.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo.
+papa|Tu as attendu ton tour.
+narrateur|Aniss pose la petite assiette, tout doux.
+narrateur|Une goutte perle au bord de l'assiette.
+narrateur|On est encore dans le jardin.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9987,7 +10601,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10151,7 +10765,10 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10179,7 +10796,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Des miettes dorées restent sur la table. Les oiseaux parlent déjà, tout loin. Aniss a encore la dînette, dans le jardin. Une petite assiette a une goutte de rosée. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10319,10 +10936,29 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Des miettes dorées restent sur la table.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Aniss a encore la dînette, dans le jardin.
+narrateur|Une petite assiette a une goutte de rosée.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10347,7 +10983,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le matin, dans le jardin. Il a joué avec la dînette. Bravo, Aniss. C'est du bon travail. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10487,7 +11123,14 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le matin, dans le jardin.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10515,7 +11158,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Aniss a encore la dînette, dans le jardin. La dînette est tiède, au soleil. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10655,7 +11298,22 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Aniss a encore la dînette, dans le jardin.
+narrateur|La dînette est tiède, au soleil.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10683,7 +11341,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu après la sieste, dans le jardin. Il a joué avec la dînette. Bravo, Aniss. C'est du bon travail. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10823,7 +11481,14 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu après la sieste, dans le jardin.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10851,7 +11516,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Aniss a encore la dînette, dans le jardin. Loin de la dînette, la pierre brille encore. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10991,10 +11656,29 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Aniss a encore la dînette, dans le jardin.
+narrateur|Loin de la dînette, la pierre brille encore.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11019,7 +11703,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le soir, dans le jardin. Il a joué avec la dînette. Bravo, Aniss. C'est du bon travail. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11159,7 +11843,14 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le soir, dans le jardin.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11187,7 +11878,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Aniss entre dans la chambre. Le rideau jaune filtre le soleil. Le doudou attend sur l'oreiller. L'oreiller sent encore le savon. Moi, je raconte le rideau. Papa parle, tout bas. Aniss lève la main. Il attend. J'ai vu l'escargot, à la fenêtre. C'est ton tour. On a attendu. Puis on parle. Bravo. Tu as levé la main. Le doudou a une oreille un peu froissée. Un carré de soleil pose sur le parquet.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11327,11 +12018,29 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Adam va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Adam se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On dit merci.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Aniss entre dans la chambre.
+narrateur|Le rideau jaune filtre le soleil.
+narrateur|Le doudou attend sur l'oreiller.
+narrateur|L'oreiller sent encore le savon.
+papa|Moi, je raconte le rideau.
+narrateur|Papa parle, tout bas.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|J'ai vu l'escargot, à la fenêtre.
+maman|C'est ton tour.
+maman|On a attendu.
+maman|Puis on parle.
+papa|Bravo.
+papa|Tu as levé la main.
+narrateur|Le doudou a une oreille un peu froissée.
+narrateur|Un carré de soleil pose sur le parquet.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>rideau</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11356,7 +12065,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Tour de parole.</t>
+          <t>Chacun son tour, près du doudou. On attend, puis on parle ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11512,7 +12221,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Tour de parole.</t>
+          <t>narrateur|Chacun son tour, près du doudou.
+papa|On attend, puis on parle ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11540,7 +12250,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>Oui. On lève la main. On attend. Puis on parle. Aniss hoche la tête. Chacun son tour. On continue, tout doux. Tu as levé la main.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11684,7 +12394,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Adam respire. Adam retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>papa|Oui.
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss hoche la tête.
+enfant-m|Chacun son tour.
+maman|On continue, tout doux.
+maman|Tu as levé la main.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11712,7 +12429,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On joue. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11876,7 +12593,11 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11904,7 +12625,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
+          <t>Aniss prend les cubes en bois. Un cube rouge fait clic. Un cube jaune sent le pin. Moi, je raconte la tour. Papa parle. Aniss lève la main. Il attend. C'est ton tour. Une maison pour l'escargot. Oui. Merci d'avoir attendu. On attend. Puis on parle. Aniss pose un cube, tout droit. Un cube tapote le parquet, tout doux. On est encore dans la chambre. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12044,10 +12765,30 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On souffle doucement. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Aniss prend les cubes en bois.
+narrateur|Un cube rouge fait clic.
+narrateur|Un cube jaune sent le pin.
+papa|Moi, je raconte la tour.
+narrateur|Papa parle.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Une maison pour l'escargot.
+maman|Oui. Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss pose un cube, tout droit.
+narrateur|Un cube tapote le parquet, tout doux.
+narrateur|On est encore dans la chambre.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12072,7 +12813,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12236,7 +12977,10 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12264,7 +13008,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Des miettes dorées restent sur la table. Les oiseaux parlent déjà, tout loin. Aniss a encore les cubes, dans la chambre. Un rayon pose sur la tour de cubes. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12404,10 +13148,29 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Des miettes dorées restent sur la table.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Aniss a encore les cubes, dans la chambre.
+narrateur|Un rayon pose sur la tour de cubes.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12432,7 +13195,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le matin, dans la chambre. Il a joué avec les cubes. Bravo, Aniss. C'est du bon travail. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12572,7 +13335,14 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le matin, dans la chambre.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12600,7 +13370,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Aniss a encore les cubes, dans la chambre. Un cube est contre l'oreiller, tout calme. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12740,7 +13510,22 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Aniss a encore les cubes, dans la chambre.
+narrateur|Un cube est contre l'oreiller, tout calme.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12768,7 +13553,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu après la sieste, dans la chambre. Il a joué avec les cubes. Bravo, Aniss. C'est du bon travail. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12908,7 +13693,14 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu après la sieste, dans la chambre.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12936,7 +13728,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Aniss a encore les cubes, dans la chambre. L'ombre des cubes danse sur le mur. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13076,10 +13868,29 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Aniss a encore les cubes, dans la chambre.
+narrateur|L'ombre des cubes danse sur le mur.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13104,7 +13915,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le soir, dans la chambre. Il a joué avec les cubes. Bravo, Aniss. C'est du bon travail. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13244,7 +14055,14 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le soir, dans la chambre.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13272,7 +14090,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Aniss ouvre le livre. La page sent le papier, un peu sec. Un dessin d'escargot est là, tout gris. Moi, je lis d'abord. Maman lit jusqu'au bout. Aniss lève la main. Il attend. Il a une coquille ronde. Oui. C'est ton tour. On a attendu. Puis on parle. Aniss caresse la page, tout léger. Bravo, Aniss. Le rideau jaune colore la page. On est encore dans la chambre. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13412,10 +14230,30 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Aniss ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Un dessin d'escargot est là, tout gris.
+maman|Moi, je lis d'abord.
+narrateur|Maman lit jusqu'au bout.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|Il a une coquille ronde.
+papa|Oui. C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+narrateur|Aniss caresse la page, tout léger.
+maman|Bravo, Aniss.
+narrateur|Le rideau jaune colore la page.
+narrateur|On est encore dans la chambre.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13440,7 +14278,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13604,7 +14442,10 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13632,7 +14473,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Des miettes dorées restent sur la table. Les oiseaux parlent déjà, tout loin. Aniss a encore le livre, dans la chambre. Le rideau filtre la page, tout jaune. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13772,10 +14613,29 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Des miettes dorées restent sur la table.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Aniss a encore le livre, dans la chambre.
+narrateur|Le rideau filtre la page, tout jaune.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13800,7 +14660,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le matin, dans la chambre. Il a joué avec le livre. Bravo, Aniss. C'est du bon travail. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13940,7 +14800,14 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le matin, dans la chambre.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13968,7 +14835,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Aniss a encore le livre, dans la chambre. Le livre est ouvert sur la couverture. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14108,7 +14975,22 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Aniss a encore le livre, dans la chambre.
+narrateur|Le livre est ouvert sur la couverture.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14136,7 +15018,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu après la sieste, dans la chambre. Il a joué avec le livre. Bravo, Aniss. C'est du bon travail. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14276,7 +15158,14 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu après la sieste, dans la chambre.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14304,7 +15193,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Aniss a encore le livre, dans la chambre. La page sent le doudou, un peu. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14444,10 +15333,29 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Aniss a encore le livre, dans la chambre.
+narrateur|La page sent le doudou, un peu.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14472,7 +15380,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le soir, dans la chambre. Il a joué avec le livre. Bravo, Aniss. C'est du bon travail. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14612,7 +15520,14 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le soir, dans la chambre.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14640,7 +15555,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+          <t>Aniss prend la dînette. Une petite assiette sonne, tout creux. Une cuillère miniature est encore tiède. Moi, je sers la soupe imaginaire. Papa parle. Aniss lève la main. Il attend. Une feuille pour l'escargot ? Oui. C'est ton tour. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Aniss pose la petite assiette, tout doux. La petite tasse est près du doudou. On est encore dans la chambre. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14780,10 +15695,31 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Adam répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Aniss prend la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+papa|Moi, je sers la soupe imaginaire.
+narrateur|Papa parle.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|Une feuille pour l'escargot ?
+maman|Oui. C'est ton tour.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo.
+papa|Tu as attendu ton tour.
+narrateur|Aniss pose la petite assiette, tout doux.
+narrateur|La petite tasse est près du doudou.
+narrateur|On est encore dans la chambre.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14808,7 +15744,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14972,7 +15908,10 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15000,7 +15939,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Des miettes dorées restent sur la table. Les oiseaux parlent déjà, tout loin. Aniss a encore la dînette, dans la chambre. Une tasse miniature est près du lit. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15140,10 +16079,29 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Des miettes dorées restent sur la table.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Aniss a encore la dînette, dans la chambre.
+narrateur|Une tasse miniature est près du lit.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15168,7 +16126,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le matin, dans la chambre. Il a joué avec la dînette. Bravo, Aniss. C'est du bon travail. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15308,7 +16266,14 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le matin, dans la chambre.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15336,7 +16301,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Aniss a encore la dînette, dans la chambre. La dînette attend au pied du lit. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15476,7 +16441,22 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Aniss a encore la dînette, dans la chambre.
+narrateur|La dînette attend au pied du lit.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15504,7 +16484,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu après la sieste, dans la chambre. Il a joué avec la dînette. Bravo, Aniss. C'est du bon travail. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15644,7 +16624,14 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu après la sieste, dans la chambre.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15672,7 +16659,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Aniss a encore la dînette, dans la chambre. Une petite assiette reflète la veilleuse. J'écoute encore un peu. Aniss lève la main. Il attend. L'escargot a une trace d'argent. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Aniss range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15812,10 +16799,29 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Adam a appris : Tour de parole. Voici le geste : lever la main ; attendre. Adam a entendu : attendre, puis parler. Adam dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Aniss a encore la dînette, dans la chambre.
+narrateur|Une petite assiette reflète la veilleuse.
+papa|J'écoute encore un peu.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|L'escargot a une trace d'argent.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15840,7 +16846,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Aniss a vécu le soir, dans la chambre. Il a joué avec la dînette. Bravo, Aniss. C'est du bon travail. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15980,7 +16986,14 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Aniss a vécu le soir, dans la chambre.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16002,7 +17015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16040,6 +17053,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-015.xlsx
+++ b/stories/arbres/TREE-COL-015.xlsx
@@ -1197,17 +1197,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Au bout d'une rue tranquille, une petite maison ouvre ses volets sur un jardin. Aniss y vit avec papa et maman. Ce matin-là, une averse vient de laver les dalles. Les feuilles brillent, et le toit laisse tomber ses dernières gouttes. Dans la cuisine, papa coupe de la menthe pour la soupe. Maman compte les assiettes pendant que la casserole frémit. En ce moment, Aniss construit un garage près de la fenêtre. Soudain, un éclair argenté traverse la pierre dehors. On dirait une route pour une toute petite voiture ! Aniss colle son nez à la vitre. Au bout de la trace avance un escargot couleur noisette. Papa ! Maman ! Venez voir ! Mais la casserole souffle au même instant. Tu disais quelque chose, Aniss ? L'escargot ! Il va disparaître ! Dehors, l'animal disparaît derrière un pot. Un rayon de soleil glisse déjà sur les dalles. Sa route va sécher. Il faut la suivre maintenant ! Aniss attend que la casserole se taise. Merci d'avoir attendu, Aniss. Montre-nous ton secret. Nous venons avec toi. Aniss enfile ses bottes. L'enquête peut commencer.</t>
+          <t>Au bout d'une rue tranquille, une petite maison ouvre ses volets sur un jardin. Aniss y vit avec papa et maman. Ce matin-là, une averse vient de laver les dalles. Les feuilles brillent, et le toit laisse tomber ses dernières gouttes. Dans la cuisine, papa coupe de la menthe pour la soupe. Maman compte les assiettes pendant que la casserole frémit. En ce moment, Aniss construit un garage près de la fenêtre. Soudain, un éclair argenté traverse la pierre dehors. On dirait une route pour une toute petite voiture ! Aniss colle son nez à la vitre. Au bout de la trace avance un escargot couleur noisette. Papa ! Maman ! Venez voir ! Mais la casserole souffle au même instant. Tu disais quelque chose, Aniss ? L'escargot ! Il va disparaître ! Dehors, l'animal disparaît derrière un pot. Un rayon de soleil glisse déjà sur les dalles. Aniss attend que la casserole se taise. Merci d'avoir attendu, Aniss. Sa route va sécher. Il faut la suivre maintenant ! Montre-nous ton secret. Nous venons avec toi. Aniss enfile ses bottes. L'enquête peut commencer.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au bout d'une rue tranquille, une petite maison ouvre ses volets sur un jardin. Aniss y vit avec papa et maman. Ce matin-là, une averse vient de laver les dalles. Les feuilles brillent, et le toit laisse tomber ses dernières gouttes. Dans la cuisine, papa coupe de la menthe pour la soupe. Maman compte les assiettes pendant que la casserole frémit. En ce moment, Aniss construit un garage près de la fenêtre. Soudain, un éclair argenté traverse la pierre dehors. On dirait une route pour une toute petite voiture ! Aniss colle son nez à la vitre. Au bout de la trace avance un escargot couleur noisette. Papa ! Maman ! Venez voir ! Mais la casserole souffle au même instant. Tu disais quelque chose, Aniss ? L'escargot ! Il va disparaître ! Dehors, l'animal disparaît derrière un pot. Un rayon de soleil glisse déjà sur les dalles. Sa route va sécher. Il faut la suivre maintenant ! Aniss attend que la casserole se taise. Merci d'avoir attendu, Aniss. Montre-nous ton secret. Nous venons avec toi. Aniss enfile ses bottes. L'enquête peut commencer.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au bout d'une rue tranquille, une petite maison ouvre ses volets sur un jardin. Aniss y vit avec papa et maman. Ce matin-là, une averse vient de laver les dalles. Les feuilles brillent, et le toit laisse tomber ses dernières gouttes. Dans la cuisine, papa coupe de la menthe pour la soupe. Maman compte les assiettes pendant que la casserole frémit. En ce moment, Aniss construit un garage près de la fenêtre. Soudain, un éclair argenté traverse la pierre dehors. On dirait une route pour une toute petite voiture ! Aniss colle son nez à la vitre. Au bout de la trace avance un escargot couleur noisette. Papa ! Maman ! Venez voir ! Mais la casserole souffle au même instant. Tu disais quelque chose, Aniss ? L'escargot ! Il va disparaître ! Dehors, l'animal disparaît derrière un pot. Un rayon de soleil glisse déjà sur les dalles. Aniss attend que la casserole se taise. Merci d'avoir attendu, Aniss. Sa route va sécher. Il faut la suivre maintenant ! Montre-nous ton secret. Nous venons avec toi. Aniss enfile ses bottes. L'enquête peut commencer.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Au bout d'une rue tranquille, une petite maison ouvre ses volets sur un jardin. Aniss y vit avec papa et maman. Ce matin-là, une averse vient de laver les dalles. Les feuilles brillent, et le toit laisse tomber ses dernières gouttes. Dans la cuisine, papa coupe de la menthe pour la soupe. Maman compte les assiettes pendant que la casserole frémit. En ce moment, Aniss construit un garage près de la fenêtre. Soudain, un éclair argenté traverse la pierre dehors. On dirait une route pour une toute petite voiture ! Aniss colle son nez à la vitre. Au bout de la trace avance un escargot couleur noisette. Papa ! Maman ! Venez voir ! Mais la casserole souffle au même instant. Tu disais quelque chose, Aniss ? L'escargot ! Il va disparaître ! Dehors, l'animal disparaît derrière un pot. Un rayon de soleil glisse déjà sur les dalles. Sa route va sécher. Il faut la suivre maintenant ! Aniss attend que la casserole se taise. Merci d'avoir attendu, Aniss. Montre-nous ton secret. Nous venons avec toi. Aniss enfile ses bottes. L'enquête peut commencer. [pause]</t>
+          <t>Au bout d'une rue tranquille, une petite maison ouvre ses volets sur un jardin. Aniss y vit avec papa et maman. Ce matin-là, une averse vient de laver les dalles. Les feuilles brillent, et le toit laisse tomber ses dernières gouttes. Dans la cuisine, papa coupe de la menthe pour la soupe. Maman compte les assiettes pendant que la casserole frémit. En ce moment, Aniss construit un garage près de la fenêtre. Soudain, un éclair argenté traverse la pierre dehors. On dirait une route pour une toute petite voiture ! Aniss colle son nez à la vitre. Au bout de la trace avance un escargot couleur noisette. Papa ! Maman ! Venez voir ! Mais la casserole souffle au même instant. Tu disais quelque chose, Aniss ? L'escargot ! Il va disparaître ! Dehors, l'animal disparaît derrière un pot. Un rayon de soleil glisse déjà sur les dalles. Aniss attend que la casserole se taise. Merci d'avoir attendu, Aniss. Sa route va sécher. Il faut la suivre maintenant ! Montre-nous ton secret. Nous venons avec toi. Aniss enfile ses bottes. L'enquête peut commencer. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
 enfant-m|Il va disparaître !
 narrateur|Dehors, l'animal disparaît derrière un pot.
 narrateur|Un rayon de soleil glisse déjà sur les dalles.
+narrateur|Aniss attend que la casserole se taise.
+papa|Merci d'avoir attendu, Aniss.
 enfant-m|Sa route va sécher.
 enfant-m|Il faut la suivre maintenant !
-narrateur|Aniss attend que la casserole se taise.
-papa|Merci d'avoir attendu, Aniss.
 maman|Montre-nous ton secret.
 maman|Nous venons avec toi.
 narrateur|Aniss enfile ses bottes.
@@ -17252,7 +17252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17309,6 +17309,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
